--- a/rag/eval/results_original120/SuppFile2_Stats_generated.xlsx
+++ b/rag/eval/results_original120/SuppFile2_Stats_generated.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IndividQuest_FisherExact(Tab3)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelComp_SignedRankFig4" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelComp_BH_AdjustFig4" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="IndividQuest_FisherExact(Tab3)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ModelComp_SignedRankFig4" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ModelComp_BH_AdjustFig4" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -707,7 +707,7 @@
         <v>7</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.18</v>
+        <v>0.232</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>10</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.757</v>
+        <v>0.737</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>6</v>
       </c>
       <c r="AJ2" s="3" t="n">
-        <v>0.0344</v>
+        <v>0.0329</v>
       </c>
       <c r="AK2" s="3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>4</v>
       </c>
       <c r="Z3" s="4" t="n">
-        <v>0.00579</v>
+        <v>0.00395</v>
       </c>
       <c r="AA3" s="4" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>1</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.013</v>
+        <v>0.0139</v>
       </c>
       <c r="AF3" s="3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>7</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.599</v>
+        <v>0.668</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>12</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.848</v>
+        <v>0.963</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>3</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0.015</v>
+        <v>0.0204</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>9</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.516</v>
+        <v>0.553</v>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>1</v>
       </c>
       <c r="AJ7" s="4" t="n">
-        <v>0.000315</v>
+        <v>0.000429</v>
       </c>
       <c r="AK7" s="4" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>6</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.28</v>
+        <v>0.382</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>8</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.615</v>
+        <v>0.58</v>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>4</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.0166</v>
+        <v>0.0226</v>
       </c>
       <c r="AK8" s="3" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>8</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.345</v>
+        <v>0.471</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>6</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.976</v>
+        <v>0.901</v>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>8</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.117</v>
+        <v>0.16</v>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>11</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.775</v>
+        <v>0.855</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>11</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.726</v>
+        <v>0.792</v>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>5</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>0.0249</v>
+        <v>0.0185</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>2</v>
       </c>
       <c r="AJ12" s="4" t="n">
-        <v>0.00151</v>
+        <v>0.00206</v>
       </c>
       <c r="AK12" s="4" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>9</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.624</v>
+        <v>0.757</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>5</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.365</v>
+        <v>0.348</v>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>5</v>
       </c>
       <c r="AJ13" s="3" t="n">
-        <v>0.0334</v>
+        <v>0.0326</v>
       </c>
       <c r="AK13" s="3" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>10</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.506</v>
+        <v>0.638</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>4</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.0721</v>
+        <v>0.0983</v>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>3</v>
       </c>
       <c r="AJ15" s="3" t="n">
-        <v>0.0118</v>
+        <v>0.0161</v>
       </c>
       <c r="AK15" s="3" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>1</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.00148</v>
+        <v>0.00201</v>
       </c>
       <c r="AA16" s="4" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>2</v>
       </c>
       <c r="AE16" s="3" t="n">
-        <v>0.0162</v>
+        <v>0.0221</v>
       </c>
       <c r="AF16" s="3" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>9</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.379</v>
+        <v>0.345</v>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>2</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>0.00192</v>
+        <v>0.00263</v>
       </c>
       <c r="AA17" s="4" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>3</v>
       </c>
       <c r="AE17" s="3" t="n">
-        <v>0.0249</v>
+        <v>0.0339</v>
       </c>
       <c r="AF17" s="3" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>7</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.113</v>
+        <v>0.141</v>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>4</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.205</v>
+        <v>0.168</v>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.112</v>
+        <v>0.106</v>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>4</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.236</v>
+        <v>0.223</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>8</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.453</v>
+        <v>0.441</v>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>7</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.611</v>
+        <v>0.624</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>7</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.488</v>
+        <v>0.549</v>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>6</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.451</v>
+        <v>0.369</v>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>9</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.848</v>
+        <v>0.963</v>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>5</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.589</v>
+        <v>0.803</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>1</v>
       </c>
       <c r="AE24" s="4" t="n">
-        <v>0.00733</v>
+        <v>0.00612</v>
       </c>
       <c r="AF24" s="4" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>1</v>
       </c>
       <c r="AJ24" s="4" t="n">
-        <v>0.000287</v>
+        <v>0.000392</v>
       </c>
       <c r="AK24" s="4" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>10</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.728</v>
+        <v>0.745</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>2</v>
       </c>
       <c r="AE25" s="3" t="n">
-        <v>0.012</v>
+        <v>0.0164</v>
       </c>
       <c r="AF25" s="3" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>2</v>
       </c>
       <c r="AJ25" s="4" t="n">
-        <v>0.00157</v>
+        <v>0.00214</v>
       </c>
       <c r="AK25" s="4" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>7</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.833</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>10</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.944</v>
+        <v>1</v>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>6</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.515</v>
+        <v>0.645</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>12</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.976</v>
+        <v>0.901</v>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>7</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.387</v>
+        <v>0.44</v>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>11</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.775</v>
+        <v>0.865</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>10</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.735</v>
+        <v>0.82</v>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>1</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.187</v>
+        <v>0.162</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>11</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.743</v>
+        <v>0.649</v>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>3</v>
       </c>
       <c r="AJ29" s="3" t="n">
-        <v>0.0201</v>
+        <v>0.0274</v>
       </c>
       <c r="AK29" s="3" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>3</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.514</v>
+        <v>0.701</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         <v>13</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.785</v>
+        <v>0.741</v>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         <v>4</v>
       </c>
       <c r="AJ30" s="3" t="n">
-        <v>0.0334</v>
+        <v>0.0326</v>
       </c>
       <c r="AK30" s="3" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>2</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.447</v>
+        <v>0.458</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>5</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.295</v>
+        <v>0.335</v>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>12</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.742</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>3</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.109</v>
+        <v>0.148</v>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>6</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.189</v>
+        <v>0.193</v>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>9</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.584</v>
+        <v>0.598</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>9</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.521</v>
+        <v>0.581</v>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>8</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.326</v>
+        <v>0.334</v>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>8</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.402</v>
+        <v>0.449</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>10</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.36</v>
+        <v>0.312</v>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>4</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.0852</v>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>9</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.23</v>
+        <v>0.209</v>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>3</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.138</v>
+        <v>0.189</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>5</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.141</v>
+        <v>0.192</v>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>13</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.9409999999999999</v>
+        <v>1</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>14</v>
       </c>
       <c r="Z41" t="n">
-        <v>1</v>
+        <v>0.906</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>6</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.848</v>
+        <v>0.963</v>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>6</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.325</v>
+        <v>0.443</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>7</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.0916</v>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>8</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.601</v>
+        <v>0.63</v>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>10</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.608</v>
+        <v>0.645</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>8</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.184</v>
+        <v>0.195</v>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>12</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.836</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>12</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.944</v>
+        <v>1</v>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>7</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.345</v>
+        <v>0.471</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>11</v>
       </c>
       <c r="AE45" t="n">
-        <v>0.976</v>
+        <v>0.901</v>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>5</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.387</v>
+        <v>0.461</v>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>4</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.0929</v>
+        <v>0.0951</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
@@ -5412,15 +5412,15 @@
       <c r="AH46" t="n">
         <v>0.0146</v>
       </c>
-      <c r="AI46" s="3" t="n">
+      <c r="AI46" t="n">
         <v>3</v>
       </c>
-      <c r="AJ46" s="3" t="n">
-        <v>0.0401</v>
-      </c>
-      <c r="AK46" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="AJ46" t="n">
+        <v>0.0548</v>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
         <v>11</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.473</v>
+        <v>0.447</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>4</v>
       </c>
       <c r="AE47" t="n">
-        <v>0.0569</v>
+        <v>0.0517</v>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>15</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.874</v>
+        <v>1</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>6</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.133</v>
+        <v>0.13</v>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>10</v>
       </c>
       <c r="AJ48" t="n">
-        <v>1</v>
+        <v>0.946</v>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>5</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.145</v>
+        <v>0.197</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>2</v>
       </c>
       <c r="AE50" s="4" t="n">
-        <v>0.000634</v>
+        <v>0.000864</v>
       </c>
       <c r="AF50" s="4" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>11</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.913</v>
+        <v>0.889</v>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         <v>2</v>
       </c>
       <c r="Z51" s="4" t="n">
-        <v>0.000187</v>
+        <v>0.000255</v>
       </c>
       <c r="AA51" s="4" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>1</v>
       </c>
       <c r="AE51" s="4" t="n">
-        <v>0.00131</v>
+        <v>0.00179</v>
       </c>
       <c r="AF51" s="4" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>1</v>
       </c>
       <c r="AJ51" s="4" t="n">
-        <v>0.000404</v>
+        <v>0.00055</v>
       </c>
       <c r="AK51" s="4" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>1</v>
       </c>
       <c r="Z52" s="4" t="n">
-        <v>8.1e-06</v>
+        <v>1.1e-05</v>
       </c>
       <c r="AA52" s="4" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>3</v>
       </c>
       <c r="AE52" s="3" t="n">
-        <v>0.0128</v>
+        <v>0.0175</v>
       </c>
       <c r="AF52" s="3" t="inlineStr">
         <is>
@@ -6090,13 +6090,13 @@
       <c r="AH52" t="n">
         <v>0.00152</v>
       </c>
-      <c r="AI52" s="4" t="n">
+      <c r="AI52" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="AJ52" s="4" t="n">
-        <v>0.008359999999999999</v>
-      </c>
-      <c r="AK52" s="4" t="inlineStr">
+      <c r="AJ52" s="3" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="AK52" s="3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -6180,7 +6180,7 @@
         <v>6</v>
       </c>
       <c r="Z54" t="n">
-        <v>0.0851</v>
+        <v>0.116</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>5</v>
       </c>
       <c r="AE54" t="n">
-        <v>0.188</v>
+        <v>0.143</v>
       </c>
       <c r="AF54" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>1</v>
       </c>
       <c r="AJ54" s="4" t="n">
-        <v>0.000246</v>
+        <v>0.00024</v>
       </c>
       <c r="AK54" s="4" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>5</v>
       </c>
       <c r="Z55" s="3" t="n">
-        <v>0.0383</v>
+        <v>0.0348</v>
       </c>
       <c r="AA55" s="3" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>4</v>
       </c>
       <c r="AE55" t="n">
-        <v>0.131</v>
+        <v>0.125</v>
       </c>
       <c r="AF55" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>11</v>
       </c>
       <c r="Z56" t="n">
-        <v>0.611</v>
+        <v>0.624</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>8</v>
       </c>
       <c r="AE56" t="n">
-        <v>0.503</v>
+        <v>0.549</v>
       </c>
       <c r="AF56" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>13</v>
       </c>
       <c r="Z57" t="n">
-        <v>0.9409999999999999</v>
+        <v>1</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
         <v>12</v>
       </c>
       <c r="Z58" t="n">
-        <v>0.972</v>
+        <v>0.737</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         <v>10</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0.848</v>
+        <v>0.963</v>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>4</v>
       </c>
       <c r="Z59" t="n">
-        <v>0.0984</v>
+        <v>0.134</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
@@ -6755,15 +6755,15 @@
       <c r="AC59" t="n">
         <v>0.0308</v>
       </c>
-      <c r="AD59" s="3" t="n">
+      <c r="AD59" t="n">
         <v>3</v>
       </c>
-      <c r="AE59" s="3" t="n">
-        <v>0.0484</v>
-      </c>
-      <c r="AF59" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="AE59" t="n">
+        <v>0.0513</v>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="AH59" t="n">
@@ -6773,7 +6773,7 @@
         <v>6</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0.217</v>
+        <v>0.23</v>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         <v>3</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.179</v>
+        <v>0.244</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>7</v>
       </c>
       <c r="AE60" t="n">
-        <v>0.418</v>
+        <v>0.456</v>
       </c>
       <c r="AF60" t="inlineStr">
         <is>
@@ -6882,15 +6882,15 @@
       <c r="AH60" t="n">
         <v>0.027</v>
       </c>
-      <c r="AI60" s="3" t="n">
+      <c r="AI60" t="n">
         <v>3</v>
       </c>
-      <c r="AJ60" s="3" t="n">
-        <v>0.0424</v>
-      </c>
-      <c r="AK60" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="AJ60" t="n">
+        <v>0.0579</v>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -7084,7 +7084,7 @@
         <v>9</v>
       </c>
       <c r="Z62" t="n">
-        <v>0.318</v>
+        <v>0.433</v>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>4</v>
       </c>
       <c r="AJ62" t="n">
-        <v>0.12</v>
+        <v>0.164</v>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
         <v>8</v>
       </c>
       <c r="Z63" t="n">
-        <v>0.0929</v>
+        <v>0.0951</v>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>9</v>
       </c>
       <c r="AE63" t="n">
-        <v>1</v>
+        <v>0.877</v>
       </c>
       <c r="AF63" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>2</v>
       </c>
       <c r="AJ63" s="3" t="n">
-        <v>0.0275</v>
+        <v>0.0375</v>
       </c>
       <c r="AK63" s="3" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>10</v>
       </c>
       <c r="AE64" t="n">
-        <v>0.869</v>
+        <v>0.846</v>
       </c>
       <c r="AF64" t="inlineStr">
         <is>
@@ -7423,7 +7423,7 @@
         <v>10</v>
       </c>
       <c r="Z65" t="n">
-        <v>0.546</v>
+        <v>0.744</v>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>5</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0.112</v>
+        <v>0.0974</v>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>7</v>
       </c>
       <c r="Z67" t="n">
-        <v>0.117</v>
+        <v>0.159</v>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>6</v>
       </c>
       <c r="AE67" t="n">
-        <v>0.174</v>
+        <v>0.237</v>
       </c>
       <c r="AF67" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>7</v>
       </c>
       <c r="AJ67" t="n">
-        <v>0.197</v>
+        <v>0.214</v>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>2</v>
       </c>
       <c r="Z68" s="4" t="n">
-        <v>1.12e-05</v>
+        <v>1.53e-05</v>
       </c>
       <c r="AA68" s="4" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         <v>1</v>
       </c>
       <c r="AE68" s="4" t="n">
-        <v>0.00251</v>
+        <v>0.00342</v>
       </c>
       <c r="AF68" s="4" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>8</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0.418</v>
+        <v>0.415</v>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>1</v>
       </c>
       <c r="Z69" s="4" t="n">
-        <v>1.37e-06</v>
+        <v>1.87e-06</v>
       </c>
       <c r="AA69" s="4" t="inlineStr">
         <is>
@@ -7885,13 +7885,13 @@
       <c r="AC69" t="n">
         <v>0.00138</v>
       </c>
-      <c r="AD69" s="4" t="n">
+      <c r="AD69" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="AE69" s="4" t="n">
-        <v>0.00759</v>
-      </c>
-      <c r="AF69" s="4" t="inlineStr">
+      <c r="AE69" s="3" t="n">
+        <v>0.0103</v>
+      </c>
+      <c r="AF69" s="3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -7903,7 +7903,7 @@
         <v>9</v>
       </c>
       <c r="AJ69" t="n">
-        <v>0.453</v>
+        <v>0.506</v>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>9</v>
       </c>
       <c r="Z72" t="n">
-        <v>0.8</v>
+        <v>0.839</v>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>9</v>
       </c>
       <c r="AE72" t="n">
-        <v>0.539</v>
+        <v>0.509</v>
       </c>
       <c r="AF72" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>3</v>
       </c>
       <c r="Z73" t="n">
-        <v>0.107</v>
+        <v>0.0969</v>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>1</v>
       </c>
       <c r="AE73" t="n">
-        <v>0.097</v>
+        <v>0.0827</v>
       </c>
       <c r="AF73" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>4</v>
       </c>
       <c r="AJ73" t="n">
-        <v>0.4</v>
+        <v>0.545</v>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>7</v>
       </c>
       <c r="Z74" t="n">
-        <v>0.651</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>8</v>
       </c>
       <c r="AE74" t="n">
-        <v>0.503</v>
+        <v>0.549</v>
       </c>
       <c r="AF74" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         <v>8</v>
       </c>
       <c r="Z75" t="n">
-        <v>0.9409999999999999</v>
+        <v>1</v>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>11</v>
       </c>
       <c r="Z77" t="n">
-        <v>0.885</v>
+        <v>0.948</v>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>4</v>
       </c>
       <c r="AE77" t="n">
-        <v>0.159</v>
+        <v>0.177</v>
       </c>
       <c r="AF77" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>7</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0.418</v>
+        <v>0.456</v>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
@@ -8668,7 +8668,7 @@
         <v>5</v>
       </c>
       <c r="Z78" t="n">
-        <v>0.608</v>
+        <v>0.645</v>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>11</v>
       </c>
       <c r="AE78" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.672</v>
       </c>
       <c r="AF78" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>5</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0.147</v>
+        <v>0.15</v>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
@@ -9003,15 +9003,15 @@
       <c r="X81" t="n">
         <v>0.0199</v>
       </c>
-      <c r="Y81" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z81" t="n">
-        <v>0.0547</v>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="Y81" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z81" s="3" t="n">
+        <v>0.0497</v>
+      </c>
+      <c r="AA81" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="AC81" t="n">
@@ -9021,7 +9021,7 @@
         <v>6</v>
       </c>
       <c r="AE81" t="n">
-        <v>0.644</v>
+        <v>0.585</v>
       </c>
       <c r="AF81" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>1</v>
       </c>
       <c r="AJ81" t="n">
-        <v>0.053</v>
+        <v>0.0722</v>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
         <v>12</v>
       </c>
       <c r="Z82" t="n">
-        <v>0.961</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>10</v>
       </c>
       <c r="AE82" t="n">
-        <v>0.743</v>
+        <v>0.675</v>
       </c>
       <c r="AF82" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>8</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0.615</v>
+        <v>0.67</v>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>5</v>
       </c>
       <c r="AE84" t="n">
-        <v>0.295</v>
+        <v>0.335</v>
       </c>
       <c r="AF84" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>6</v>
       </c>
       <c r="AJ84" t="n">
-        <v>0.8070000000000001</v>
+        <v>1</v>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         <v>6</v>
       </c>
       <c r="Z85" t="n">
-        <v>0.506</v>
+        <v>0.638</v>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>3</v>
       </c>
       <c r="AE85" t="n">
-        <v>0.149</v>
+        <v>0.203</v>
       </c>
       <c r="AF85" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>10</v>
       </c>
       <c r="AJ85" t="n">
-        <v>0.802</v>
+        <v>0.757</v>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>4</v>
       </c>
       <c r="Z86" t="n">
-        <v>0.159</v>
+        <v>0.189</v>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>2</v>
       </c>
       <c r="AE86" t="n">
-        <v>0.128</v>
+        <v>0.175</v>
       </c>
       <c r="AF86" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
         <v>3</v>
       </c>
       <c r="AJ86" t="n">
-        <v>0.216</v>
+        <v>0.21</v>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>2</v>
       </c>
       <c r="Z87" t="n">
-        <v>0.0552</v>
+        <v>0.0658</v>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         <v>7</v>
       </c>
       <c r="AE87" t="n">
-        <v>0.542</v>
+        <v>0.739</v>
       </c>
       <c r="AF87" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>2</v>
       </c>
       <c r="AJ87" t="n">
-        <v>0.129</v>
+        <v>0.141</v>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>5</v>
       </c>
       <c r="Z89" t="n">
-        <v>0.122</v>
+        <v>0.166</v>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>1</v>
       </c>
       <c r="AE89" s="4" t="n">
-        <v>9.789999999999999e-05</v>
+        <v>0.000133</v>
       </c>
       <c r="AF89" s="4" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>2</v>
       </c>
       <c r="AJ89" s="4" t="n">
-        <v>0.000143</v>
+        <v>9.75e-05</v>
       </c>
       <c r="AK89" s="4" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>4</v>
       </c>
       <c r="Z90" t="n">
-        <v>0.103</v>
+        <v>0.0969</v>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>9</v>
       </c>
       <c r="AE90" t="n">
-        <v>0.259</v>
+        <v>0.245</v>
       </c>
       <c r="AF90" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>9</v>
       </c>
       <c r="Z92" t="n">
-        <v>0.9409999999999999</v>
+        <v>1</v>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>8</v>
       </c>
       <c r="AE92" t="n">
-        <v>0.352</v>
+        <v>0.48</v>
       </c>
       <c r="AF92" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
         <v>4</v>
       </c>
       <c r="AE93" s="3" t="n">
-        <v>0.0412</v>
+        <v>0.0281</v>
       </c>
       <c r="AF93" s="3" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>7</v>
       </c>
       <c r="AJ93" t="n">
-        <v>0.191</v>
+        <v>0.261</v>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
         <v>7</v>
       </c>
       <c r="Z94" t="n">
-        <v>0.506</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
@@ -10378,7 +10378,7 @@
         <v>2</v>
       </c>
       <c r="AE94" s="3" t="n">
-        <v>0.0214</v>
+        <v>0.0195</v>
       </c>
       <c r="AF94" s="3" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>4</v>
       </c>
       <c r="AJ94" s="4" t="n">
-        <v>0.00141</v>
+        <v>0.00161</v>
       </c>
       <c r="AK94" s="4" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>3</v>
       </c>
       <c r="AE95" s="3" t="n">
-        <v>0.0379</v>
+        <v>0.0345</v>
       </c>
       <c r="AF95" s="3" t="inlineStr">
         <is>
@@ -10505,7 +10505,7 @@
         <v>3</v>
       </c>
       <c r="AJ95" s="4" t="n">
-        <v>0.00183</v>
+        <v>0.00249</v>
       </c>
       <c r="AK95" s="4" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>2</v>
       </c>
       <c r="Z96" s="3" t="n">
-        <v>0.0177</v>
+        <v>0.0242</v>
       </c>
       <c r="AA96" s="3" t="inlineStr">
         <is>
@@ -10604,7 +10604,7 @@
         <v>11</v>
       </c>
       <c r="AE96" t="n">
-        <v>0.944</v>
+        <v>1</v>
       </c>
       <c r="AF96" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>1</v>
       </c>
       <c r="Z97" s="4" t="n">
-        <v>0.00293</v>
+        <v>0.00399</v>
       </c>
       <c r="AA97" s="4" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>12</v>
       </c>
       <c r="AE97" t="n">
-        <v>0.976</v>
+        <v>0.901</v>
       </c>
       <c r="AF97" t="inlineStr">
         <is>
@@ -10731,7 +10731,7 @@
         <v>1</v>
       </c>
       <c r="AJ97" s="4" t="n">
-        <v>3.77e-05</v>
+        <v>5.15e-05</v>
       </c>
       <c r="AK97" s="4" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>10</v>
       </c>
       <c r="AE98" t="n">
-        <v>0.968</v>
+        <v>0.733</v>
       </c>
       <c r="AF98" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>12</v>
       </c>
       <c r="AJ98" t="n">
-        <v>0.819</v>
+        <v>0.85</v>
       </c>
       <c r="AK98" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>3</v>
       </c>
       <c r="Z99" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.0593</v>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
@@ -10943,7 +10943,7 @@
         <v>5</v>
       </c>
       <c r="AE99" t="n">
-        <v>0.0569</v>
+        <v>0.0517</v>
       </c>
       <c r="AF99" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>8</v>
       </c>
       <c r="Z100" t="n">
-        <v>0.624</v>
+        <v>0.757</v>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>6</v>
       </c>
       <c r="AE100" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.0888</v>
       </c>
       <c r="AF100" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>6</v>
       </c>
       <c r="AJ100" s="3" t="n">
-        <v>0.015</v>
+        <v>0.0122</v>
       </c>
       <c r="AK100" s="3" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>6</v>
       </c>
       <c r="Z102" t="n">
-        <v>0.289</v>
+        <v>0.394</v>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
@@ -11282,7 +11282,7 @@
         <v>7</v>
       </c>
       <c r="AE102" t="n">
-        <v>0.14</v>
+        <v>0.191</v>
       </c>
       <c r="AF102" t="inlineStr">
         <is>
@@ -11296,7 +11296,7 @@
         <v>5</v>
       </c>
       <c r="AJ102" s="3" t="n">
-        <v>0.0103</v>
+        <v>0.0141</v>
       </c>
       <c r="AK102" s="3" t="inlineStr">
         <is>
@@ -11409,7 +11409,7 @@
         <v>8</v>
       </c>
       <c r="AJ103" t="n">
-        <v>0.216</v>
+        <v>0.201</v>
       </c>
       <c r="AK103" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>10</v>
       </c>
       <c r="Z104" t="n">
-        <v>0.768</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         <v>13</v>
       </c>
       <c r="AE104" t="n">
-        <v>0.915</v>
+        <v>1</v>
       </c>
       <c r="AF104" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
         <v>13</v>
       </c>
       <c r="AJ104" t="n">
-        <v>0.823</v>
+        <v>0.882</v>
       </c>
       <c r="AK104" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>9</v>
       </c>
       <c r="I2" t="n">
-        <v>0.496</v>
+        <v>0.506</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.00116</v>
+        <v>0.00118</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.000179</v>
+        <v>0.000163</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -15676,7 +15676,7 @@
         <v>7</v>
       </c>
       <c r="X2" t="n">
-        <v>0.522</v>
+        <v>0.53</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00227</v>
+        <v>0.00242</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>7</v>
       </c>
       <c r="N3" t="n">
-        <v>0.205</v>
+        <v>0.208</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -15741,7 +15741,7 @@
         <v>3</v>
       </c>
       <c r="S3" t="n">
-        <v>0.00545</v>
+        <v>0.00625</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00118</v>
+        <v>0.00125</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -15792,7 +15792,7 @@
         <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00648</v>
+        <v>0.00723</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>6</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.0683</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>2</v>
       </c>
       <c r="S4" t="n">
-        <v>0.00472</v>
+        <v>0.00527</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>0.00472</v>
+        <v>0.00532</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>7</v>
       </c>
       <c r="I5" t="n">
-        <v>0.427</v>
+        <v>0.431</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>0.00472</v>
+        <v>0.00532</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>7</v>
       </c>
       <c r="S5" t="n">
-        <v>0.066</v>
+        <v>0.0675</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>9</v>
       </c>
       <c r="X5" t="n">
-        <v>0.917</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0179</v>
+        <v>0.0188</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>8</v>
       </c>
       <c r="N6" t="n">
-        <v>0.208</v>
+        <v>0.215</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -15978,7 +15978,7 @@
         <v>5</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0295</v>
+        <v>0.0308</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         <v>3</v>
       </c>
       <c r="X6" t="n">
-        <v>0.00472</v>
+        <v>0.00537</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -16029,7 +16029,7 @@
         <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0091</v>
+        <v>0.00983</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>0.00472</v>
+        <v>0.00537</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -16057,7 +16057,7 @@
         <v>9</v>
       </c>
       <c r="S7" t="n">
-        <v>0.889</v>
+        <v>0.899</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -16071,7 +16071,7 @@
         <v>4</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0242</v>
+        <v>0.025</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -16108,7 +16108,7 @@
         <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>0.448</v>
+        <v>0.455</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>5</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0345</v>
+        <v>0.0367</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -16136,7 +16136,7 @@
         <v>4</v>
       </c>
       <c r="S8" t="n">
-        <v>0.00648</v>
+        <v>0.00723</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>6</v>
       </c>
       <c r="X8" t="n">
-        <v>0.496</v>
+        <v>0.506</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -16187,7 +16187,7 @@
         <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>0.107</v>
+        <v>0.11</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -16201,7 +16201,7 @@
         <v>4</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0204</v>
+        <v>0.0209</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>8</v>
       </c>
       <c r="S9" t="n">
-        <v>0.208</v>
+        <v>0.215</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -16229,7 +16229,7 @@
         <v>8</v>
       </c>
       <c r="X9" t="n">
-        <v>0.624</v>
+        <v>0.639</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0323</v>
+        <v>0.0341</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
         <v>9</v>
       </c>
       <c r="N10" t="n">
-        <v>0.397</v>
+        <v>0.398</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>6</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0608</v>
+        <v>0.0615</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.0849</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>7</v>
       </c>
       <c r="I12" t="n">
-        <v>0.297</v>
+        <v>0.298</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>0.00319</v>
+        <v>0.00261</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0037</v>
+        <v>0.00404</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -16388,7 +16388,7 @@
         <v>7</v>
       </c>
       <c r="X12" t="n">
-        <v>0.618</v>
+        <v>0.624</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -16425,7 +16425,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0037</v>
+        <v>0.00404</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>9</v>
       </c>
       <c r="N13" t="n">
-        <v>0.733</v>
+        <v>0.745</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -16453,7 +16453,7 @@
         <v>3</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0127</v>
+        <v>0.0138</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -16467,7 +16467,7 @@
         <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0037</v>
+        <v>0.00404</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0178</v>
+        <v>0.0198</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -16518,11 +16518,11 @@
         <v>5</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0491</v>
+        <v>0.0519</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="Q14" t="n">
@@ -16532,7 +16532,7 @@
         <v>2</v>
       </c>
       <c r="S14" t="n">
-        <v>0.00874</v>
+        <v>0.00894</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -16546,7 +16546,7 @@
         <v>2</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0037</v>
+        <v>0.00404</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>8</v>
       </c>
       <c r="I15" t="n">
-        <v>0.434</v>
+        <v>0.429</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -16597,7 +16597,7 @@
         <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0037</v>
+        <v>0.00404</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -16611,7 +16611,7 @@
         <v>6</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0813</v>
+        <v>0.0832</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -16662,7 +16662,7 @@
         <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>0.00498</v>
+        <v>0.00551</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>0.00563</v>
+        <v>0.00597</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>9</v>
       </c>
       <c r="S16" t="n">
-        <v>0.977</v>
+        <v>0.971</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>3</v>
       </c>
       <c r="X16" t="n">
-        <v>0.00924</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -16741,7 +16741,7 @@
         <v>6</v>
       </c>
       <c r="I17" t="n">
-        <v>0.139</v>
+        <v>0.143</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>0.00976</v>
+        <v>0.0103</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -16769,7 +16769,7 @@
         <v>8</v>
       </c>
       <c r="S17" t="n">
-        <v>0.186</v>
+        <v>0.196</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>8</v>
       </c>
       <c r="X17" t="n">
-        <v>0.977</v>
+        <v>0.971</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>0.01</v>
+        <v>0.0107</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>7</v>
       </c>
       <c r="N18" t="n">
-        <v>0.167</v>
+        <v>0.174</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -16848,7 +16848,7 @@
         <v>5</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0253</v>
+        <v>0.0273</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>4</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0119</v>
+        <v>0.0129</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -16899,7 +16899,7 @@
         <v>9</v>
       </c>
       <c r="I19" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
         <v>6</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0699</v>
+        <v>0.0708</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -16927,7 +16927,7 @@
         <v>4</v>
       </c>
       <c r="S19" t="n">
-        <v>0.016</v>
+        <v>0.0177</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -16941,7 +16941,7 @@
         <v>6</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6</v>
+        <v>0.602</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>5</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0699</v>
+        <v>0.0708</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -16992,7 +16992,7 @@
         <v>7</v>
       </c>
       <c r="N20" t="n">
-        <v>0.167</v>
+        <v>0.174</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -17006,7 +17006,7 @@
         <v>7</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0858</v>
+        <v>0.0885</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
         <v>5</v>
       </c>
       <c r="X20" t="n">
-        <v>0.105</v>
+        <v>0.109</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>

--- a/rag/eval/results_original120/SuppFile2_Stats_generated.xlsx
+++ b/rag/eval/results_original120/SuppFile2_Stats_generated.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="IndividQuest_FisherExact(Tab3)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ModelComp_SignedRankFig4" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ModelComp_BH_AdjustFig4" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IndividQuest_FisherExact(Tab3)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelComp_SignedRankFig4" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelComp_BH_AdjustFig4" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1782,7 +1782,7 @@
         <v>11</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.792</v>
+        <v>0.66</v>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>10</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.82</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>12</v>
       </c>
       <c r="AJ98" t="n">
-        <v>0.85</v>
+        <v>0.819</v>
       </c>
       <c r="AK98" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>9</v>
       </c>
       <c r="I2" t="n">
-        <v>0.506</v>
+        <v>0.501</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00242</v>
+        <v>0.00255</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00125</v>
+        <v>0.00121</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>8</v>
       </c>
       <c r="N6" t="n">
-        <v>0.215</v>
+        <v>0.21</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>5</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0367</v>
+        <v>0.0356</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>6</v>
       </c>
       <c r="X8" t="n">
-        <v>0.506</v>
+        <v>0.501</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -16201,7 +16201,7 @@
         <v>4</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0209</v>
+        <v>0.021</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>8</v>
       </c>
       <c r="S9" t="n">
-        <v>0.215</v>
+        <v>0.21</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
         <v>9</v>
       </c>
       <c r="N10" t="n">
-        <v>0.398</v>
+        <v>0.406</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>7</v>
       </c>
       <c r="I12" t="n">
-        <v>0.298</v>
+        <v>0.304</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>9</v>
       </c>
       <c r="N13" t="n">
-        <v>0.745</v>
+        <v>0.743</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -16769,7 +16769,7 @@
         <v>8</v>
       </c>
       <c r="S17" t="n">
-        <v>0.196</v>
+        <v>0.192</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -16848,7 +16848,7 @@
         <v>5</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0273</v>
+        <v>0.0264</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>

--- a/rag/eval/results_original120/SuppFile2_Stats_generated.xlsx
+++ b/rag/eval/results_original120/SuppFile2_Stats_generated.xlsx
@@ -707,7 +707,7 @@
         <v>7</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.232</v>
+        <v>0.209</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>10</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.737</v>
+        <v>0.751</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>6</v>
       </c>
       <c r="AJ2" s="3" t="n">
-        <v>0.0329</v>
+        <v>0.0375</v>
       </c>
       <c r="AK2" s="3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>4</v>
       </c>
       <c r="Z3" s="4" t="n">
-        <v>0.00395</v>
+        <v>0.00474</v>
       </c>
       <c r="AA3" s="4" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>1</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.0139</v>
+        <v>0.0142</v>
       </c>
       <c r="AF3" s="3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>7</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.668</v>
+        <v>0.653</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>12</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.963</v>
+        <v>0.896</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>3</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0.0204</v>
+        <v>0.0163</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>9</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.553</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>1</v>
       </c>
       <c r="AJ7" s="4" t="n">
-        <v>0.000429</v>
+        <v>0.000343</v>
       </c>
       <c r="AK7" s="4" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>6</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.382</v>
+        <v>0.305</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>8</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.58</v>
+        <v>0.604</v>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>4</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.0226</v>
+        <v>0.0217</v>
       </c>
       <c r="AK8" s="3" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>8</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.471</v>
+        <v>0.377</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>6</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.901</v>
+        <v>0.865</v>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>8</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.16</v>
+        <v>0.128</v>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>11</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.855</v>
+        <v>0.845</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>11</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.66</v>
+        <v>0.704</v>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>5</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>0.0185</v>
+        <v>0.0197</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>2</v>
       </c>
       <c r="AJ12" s="4" t="n">
-        <v>0.00206</v>
+        <v>0.00165</v>
       </c>
       <c r="AK12" s="4" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>9</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.757</v>
+        <v>0.778</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>5</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.348</v>
+        <v>0.398</v>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>5</v>
       </c>
       <c r="AJ13" s="3" t="n">
-        <v>0.0326</v>
+        <v>0.0365</v>
       </c>
       <c r="AK13" s="3" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>10</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.638</v>
+        <v>0.621</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>4</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.0983</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>3</v>
       </c>
       <c r="AJ15" s="3" t="n">
-        <v>0.0161</v>
+        <v>0.016</v>
       </c>
       <c r="AK15" s="3" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>1</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.00201</v>
+        <v>0.00161</v>
       </c>
       <c r="AA16" s="4" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>2</v>
       </c>
       <c r="AE16" s="3" t="n">
-        <v>0.0221</v>
+        <v>0.0177</v>
       </c>
       <c r="AF16" s="3" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>9</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.345</v>
+        <v>0.31</v>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>2</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>0.00263</v>
+        <v>0.00252</v>
       </c>
       <c r="AA17" s="4" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>3</v>
       </c>
       <c r="AE17" s="3" t="n">
-        <v>0.0339</v>
+        <v>0.0321</v>
       </c>
       <c r="AF17" s="3" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>7</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.141</v>
+        <v>0.123</v>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>4</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.168</v>
+        <v>0.192</v>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.106</v>
+        <v>0.11</v>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>4</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.223</v>
+        <v>0.232</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>8</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.441</v>
+        <v>0.449</v>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>7</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.624</v>
+        <v>0.666</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>7</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.549</v>
+        <v>0.532</v>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>6</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.369</v>
+        <v>0.422</v>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>9</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.963</v>
+        <v>0.89</v>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>5</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.803</v>
+        <v>0.642</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>1</v>
       </c>
       <c r="AE24" s="4" t="n">
-        <v>0.00612</v>
+        <v>0.008</v>
       </c>
       <c r="AF24" s="4" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>1</v>
       </c>
       <c r="AJ24" s="4" t="n">
-        <v>0.000392</v>
+        <v>0.000313</v>
       </c>
       <c r="AK24" s="4" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>10</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.745</v>
+        <v>0.65</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>2</v>
       </c>
       <c r="AE25" s="3" t="n">
-        <v>0.0164</v>
+        <v>0.0197</v>
       </c>
       <c r="AF25" s="3" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>2</v>
       </c>
       <c r="AJ25" s="4" t="n">
-        <v>0.00214</v>
+        <v>0.00299</v>
       </c>
       <c r="AK25" s="4" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>7</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.833</v>
+        <v>0.892</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>6</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.645</v>
+        <v>0.516</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>12</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.901</v>
+        <v>0.865</v>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>7</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.44</v>
+        <v>0.352</v>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>11</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.865</v>
+        <v>0.845</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>10</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.721</v>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>1</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.162</v>
+        <v>0.178</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>11</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.649</v>
+        <v>0.714</v>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>3</v>
       </c>
       <c r="AJ29" s="3" t="n">
-        <v>0.0274</v>
+        <v>0.0219</v>
       </c>
       <c r="AK29" s="3" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>3</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.701</v>
+        <v>0.744</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         <v>13</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.741</v>
+        <v>0.77</v>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         <v>4</v>
       </c>
       <c r="AJ30" s="3" t="n">
-        <v>0.0326</v>
+        <v>0.0365</v>
       </c>
       <c r="AK30" s="3" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>2</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.458</v>
+        <v>0.732</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>5</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.335</v>
+        <v>0.402</v>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>12</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.742</v>
+        <v>0.756</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>3</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.148</v>
+        <v>0.138</v>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>6</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.193</v>
+        <v>0.206</v>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>9</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.598</v>
+        <v>0.574</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>9</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.581</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>8</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.334</v>
+        <v>0.356</v>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>8</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.449</v>
+        <v>0.395</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>10</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.312</v>
+        <v>0.344</v>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>4</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.0852</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>9</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.209</v>
+        <v>0.223</v>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>3</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.189</v>
+        <v>0.201</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>5</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.192</v>
+        <v>0.204</v>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>7</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1</v>
+        <v>0.966</v>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>14</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.906</v>
+        <v>1</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>6</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.963</v>
+        <v>0.89</v>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>6</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.443</v>
+        <v>0.354</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>7</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.0916</v>
+        <v>0.0917</v>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>8</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.63</v>
+        <v>0.596</v>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>10</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.645</v>
+        <v>0.581</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>8</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.195</v>
+        <v>0.201</v>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>12</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.836</v>
+        <v>0.892</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>7</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.471</v>
+        <v>0.377</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>11</v>
       </c>
       <c r="AE45" t="n">
-        <v>0.901</v>
+        <v>0.865</v>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>5</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.461</v>
+        <v>0.369</v>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>4</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.0951</v>
+        <v>0.101</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         <v>3</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0.0548</v>
+        <v>0.0584</v>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>11</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.447</v>
+        <v>0.464</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>4</v>
       </c>
       <c r="AE47" t="n">
-        <v>0.0517</v>
+        <v>0.0621</v>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>15</v>
       </c>
       <c r="Z48" t="n">
-        <v>1</v>
+        <v>0.983</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>6</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.13</v>
+        <v>0.145</v>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>10</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0.946</v>
+        <v>0.984</v>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>11</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.889</v>
+        <v>0.905</v>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         <v>2</v>
       </c>
       <c r="Z51" s="4" t="n">
-        <v>0.000255</v>
+        <v>0.000204</v>
       </c>
       <c r="AA51" s="4" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>1</v>
       </c>
       <c r="AE51" s="4" t="n">
-        <v>0.00179</v>
+        <v>0.00143</v>
       </c>
       <c r="AF51" s="4" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>1</v>
       </c>
       <c r="AJ51" s="4" t="n">
-        <v>0.00055</v>
+        <v>0.00044</v>
       </c>
       <c r="AK51" s="4" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>1</v>
       </c>
       <c r="Z52" s="4" t="n">
-        <v>1.1e-05</v>
+        <v>8.84e-06</v>
       </c>
       <c r="AA52" s="4" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>3</v>
       </c>
       <c r="AE52" s="3" t="n">
-        <v>0.0175</v>
+        <v>0.014</v>
       </c>
       <c r="AF52" s="3" t="inlineStr">
         <is>
@@ -6090,13 +6090,13 @@
       <c r="AH52" t="n">
         <v>0.00152</v>
       </c>
-      <c r="AI52" s="3" t="n">
+      <c r="AI52" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="AJ52" s="3" t="n">
-        <v>0.0114</v>
-      </c>
-      <c r="AK52" s="3" t="inlineStr">
+      <c r="AJ52" s="4" t="n">
+        <v>0.00912</v>
+      </c>
+      <c r="AK52" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -6194,7 +6194,7 @@
         <v>5</v>
       </c>
       <c r="AE54" t="n">
-        <v>0.143</v>
+        <v>0.171</v>
       </c>
       <c r="AF54" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>1</v>
       </c>
       <c r="AJ54" s="4" t="n">
-        <v>0.00024</v>
+        <v>0.000269</v>
       </c>
       <c r="AK54" s="4" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>5</v>
       </c>
       <c r="Z55" s="3" t="n">
-        <v>0.0348</v>
+        <v>0.0358</v>
       </c>
       <c r="AA55" s="3" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>11</v>
       </c>
       <c r="Z56" t="n">
-        <v>0.624</v>
+        <v>0.666</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>11</v>
       </c>
       <c r="AJ57" t="n">
-        <v>1</v>
+        <v>0.966</v>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
         <v>12</v>
       </c>
       <c r="Z58" t="n">
-        <v>0.737</v>
+        <v>0.884</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         <v>10</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0.963</v>
+        <v>0.89</v>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>4</v>
       </c>
       <c r="Z59" t="n">
-        <v>0.134</v>
+        <v>0.107</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         <v>3</v>
       </c>
       <c r="AE59" t="n">
-        <v>0.0513</v>
+        <v>0.0528</v>
       </c>
       <c r="AF59" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>6</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0.23</v>
+        <v>0.237</v>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         <v>3</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.244</v>
+        <v>0.196</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>3</v>
       </c>
       <c r="AJ60" t="n">
-        <v>0.0579</v>
+        <v>0.054</v>
       </c>
       <c r="AK60" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>9</v>
       </c>
       <c r="Z62" t="n">
-        <v>0.433</v>
+        <v>0.346</v>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>4</v>
       </c>
       <c r="AJ62" t="n">
-        <v>0.164</v>
+        <v>0.131</v>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
         <v>8</v>
       </c>
       <c r="Z63" t="n">
-        <v>0.0951</v>
+        <v>0.101</v>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>9</v>
       </c>
       <c r="AE63" t="n">
-        <v>0.877</v>
+        <v>0.965</v>
       </c>
       <c r="AF63" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>2</v>
       </c>
       <c r="AJ63" s="3" t="n">
-        <v>0.0375</v>
+        <v>0.045</v>
       </c>
       <c r="AK63" s="3" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>10</v>
       </c>
       <c r="AE64" t="n">
-        <v>0.846</v>
+        <v>0.862</v>
       </c>
       <c r="AF64" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>5</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0.0974</v>
+        <v>0.107</v>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>7</v>
       </c>
       <c r="Z67" t="n">
-        <v>0.159</v>
+        <v>0.17</v>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>6</v>
       </c>
       <c r="AE67" t="n">
-        <v>0.237</v>
+        <v>0.211</v>
       </c>
       <c r="AF67" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>2</v>
       </c>
       <c r="Z68" s="4" t="n">
-        <v>1.53e-05</v>
+        <v>1.22e-05</v>
       </c>
       <c r="AA68" s="4" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         <v>1</v>
       </c>
       <c r="AE68" s="4" t="n">
-        <v>0.00342</v>
+        <v>0.00274</v>
       </c>
       <c r="AF68" s="4" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>8</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0.415</v>
+        <v>0.365</v>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>1</v>
       </c>
       <c r="Z69" s="4" t="n">
-        <v>1.87e-06</v>
+        <v>1.49e-06</v>
       </c>
       <c r="AA69" s="4" t="inlineStr">
         <is>
@@ -7885,13 +7885,13 @@
       <c r="AC69" t="n">
         <v>0.00138</v>
       </c>
-      <c r="AD69" s="3" t="n">
+      <c r="AD69" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="AE69" s="3" t="n">
-        <v>0.0103</v>
-      </c>
-      <c r="AF69" s="3" t="inlineStr">
+      <c r="AE69" s="4" t="n">
+        <v>0.008279999999999999</v>
+      </c>
+      <c r="AF69" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -7903,7 +7903,7 @@
         <v>9</v>
       </c>
       <c r="AJ69" t="n">
-        <v>0.506</v>
+        <v>0.495</v>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>9</v>
       </c>
       <c r="Z72" t="n">
-        <v>0.839</v>
+        <v>0.793</v>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>9</v>
       </c>
       <c r="AE72" t="n">
-        <v>0.509</v>
+        <v>0.529</v>
       </c>
       <c r="AF72" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>3</v>
       </c>
       <c r="Z73" t="n">
-        <v>0.0969</v>
+        <v>0.103</v>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>1</v>
       </c>
       <c r="AE73" t="n">
-        <v>0.0827</v>
+        <v>0.0882</v>
       </c>
       <c r="AF73" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>4</v>
       </c>
       <c r="AJ73" t="n">
-        <v>0.545</v>
+        <v>0.436</v>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>7</v>
       </c>
       <c r="Z74" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>9</v>
       </c>
       <c r="AJ75" t="n">
-        <v>1</v>
+        <v>0.977</v>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>11</v>
       </c>
       <c r="Z77" t="n">
-        <v>0.948</v>
+        <v>0.965</v>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>4</v>
       </c>
       <c r="AE77" t="n">
-        <v>0.177</v>
+        <v>0.173</v>
       </c>
       <c r="AF77" t="inlineStr">
         <is>
@@ -8668,7 +8668,7 @@
         <v>5</v>
       </c>
       <c r="Z78" t="n">
-        <v>0.645</v>
+        <v>0.581</v>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>11</v>
       </c>
       <c r="AE78" t="n">
-        <v>0.672</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="AF78" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>5</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0.15</v>
+        <v>0.144</v>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
@@ -9003,15 +9003,15 @@
       <c r="X81" t="n">
         <v>0.0199</v>
       </c>
-      <c r="Y81" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z81" s="3" t="n">
-        <v>0.0497</v>
-      </c>
-      <c r="AA81" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="Y81" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>0.0597</v>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="AC81" t="n">
@@ -9021,7 +9021,7 @@
         <v>6</v>
       </c>
       <c r="AE81" t="n">
-        <v>0.585</v>
+        <v>0.702</v>
       </c>
       <c r="AF81" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>1</v>
       </c>
       <c r="AJ81" t="n">
-        <v>0.0722</v>
+        <v>0.0694</v>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
         <v>12</v>
       </c>
       <c r="Z82" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.953</v>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>10</v>
       </c>
       <c r="AE82" t="n">
-        <v>0.675</v>
+        <v>0.72</v>
       </c>
       <c r="AF82" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>5</v>
       </c>
       <c r="AE84" t="n">
-        <v>0.335</v>
+        <v>0.402</v>
       </c>
       <c r="AF84" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>6</v>
       </c>
       <c r="AJ84" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         <v>6</v>
       </c>
       <c r="Z85" t="n">
-        <v>0.638</v>
+        <v>0.621</v>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>3</v>
       </c>
       <c r="AE85" t="n">
-        <v>0.203</v>
+        <v>0.183</v>
       </c>
       <c r="AF85" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>10</v>
       </c>
       <c r="AJ85" t="n">
-        <v>0.757</v>
+        <v>0.787</v>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>4</v>
       </c>
       <c r="Z86" t="n">
-        <v>0.189</v>
+        <v>0.173</v>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>2</v>
       </c>
       <c r="AE86" t="n">
-        <v>0.175</v>
+        <v>0.14</v>
       </c>
       <c r="AF86" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
         <v>3</v>
       </c>
       <c r="AJ86" t="n">
-        <v>0.21</v>
+        <v>0.196</v>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>2</v>
       </c>
       <c r="Z87" t="n">
-        <v>0.0658</v>
+        <v>0.0602</v>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         <v>7</v>
       </c>
       <c r="AE87" t="n">
-        <v>0.739</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AF87" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>5</v>
       </c>
       <c r="Z89" t="n">
-        <v>0.166</v>
+        <v>0.155</v>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>1</v>
       </c>
       <c r="AE89" s="4" t="n">
-        <v>0.000133</v>
+        <v>0.000142</v>
       </c>
       <c r="AF89" s="4" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>2</v>
       </c>
       <c r="AJ89" s="4" t="n">
-        <v>9.75e-05</v>
+        <v>7.8e-05</v>
       </c>
       <c r="AK89" s="4" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>4</v>
       </c>
       <c r="Z90" t="n">
-        <v>0.0969</v>
+        <v>0.0985</v>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>9</v>
       </c>
       <c r="AE90" t="n">
-        <v>0.245</v>
+        <v>0.254</v>
       </c>
       <c r="AF90" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>8</v>
       </c>
       <c r="AE92" t="n">
-        <v>0.48</v>
+        <v>0.512</v>
       </c>
       <c r="AF92" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         <v>10</v>
       </c>
       <c r="AJ92" t="n">
-        <v>1</v>
+        <v>0.966</v>
       </c>
       <c r="AK92" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
         <v>4</v>
       </c>
       <c r="AE93" s="3" t="n">
-        <v>0.0281</v>
+        <v>0.036</v>
       </c>
       <c r="AF93" s="3" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>7</v>
       </c>
       <c r="AJ93" t="n">
-        <v>0.261</v>
+        <v>0.209</v>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
         <v>7</v>
       </c>
       <c r="Z94" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.552</v>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
@@ -10378,7 +10378,7 @@
         <v>2</v>
       </c>
       <c r="AE94" s="3" t="n">
-        <v>0.0195</v>
+        <v>0.0234</v>
       </c>
       <c r="AF94" s="3" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>4</v>
       </c>
       <c r="AJ94" s="4" t="n">
-        <v>0.00161</v>
+        <v>0.00146</v>
       </c>
       <c r="AK94" s="4" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>3</v>
       </c>
       <c r="AE95" s="3" t="n">
-        <v>0.0345</v>
+        <v>0.0414</v>
       </c>
       <c r="AF95" s="3" t="inlineStr">
         <is>
@@ -10505,7 +10505,7 @@
         <v>3</v>
       </c>
       <c r="AJ95" s="4" t="n">
-        <v>0.00249</v>
+        <v>0.00299</v>
       </c>
       <c r="AK95" s="4" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>2</v>
       </c>
       <c r="Z96" s="3" t="n">
-        <v>0.0242</v>
+        <v>0.029</v>
       </c>
       <c r="AA96" s="3" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>1</v>
       </c>
       <c r="Z97" s="4" t="n">
-        <v>0.00399</v>
+        <v>0.00319</v>
       </c>
       <c r="AA97" s="4" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>12</v>
       </c>
       <c r="AE97" t="n">
-        <v>0.901</v>
+        <v>0.865</v>
       </c>
       <c r="AF97" t="inlineStr">
         <is>
@@ -10731,7 +10731,7 @@
         <v>1</v>
       </c>
       <c r="AJ97" s="4" t="n">
-        <v>5.15e-05</v>
+        <v>4.12e-05</v>
       </c>
       <c r="AK97" s="4" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>10</v>
       </c>
       <c r="AE98" t="n">
-        <v>0.733</v>
+        <v>0.88</v>
       </c>
       <c r="AF98" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>3</v>
       </c>
       <c r="Z99" t="n">
-        <v>0.0593</v>
+        <v>0.0677</v>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
@@ -10943,7 +10943,7 @@
         <v>5</v>
       </c>
       <c r="AE99" t="n">
-        <v>0.0517</v>
+        <v>0.0621</v>
       </c>
       <c r="AF99" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>8</v>
       </c>
       <c r="Z100" t="n">
-        <v>0.757</v>
+        <v>0.778</v>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>6</v>
       </c>
       <c r="AE100" t="n">
-        <v>0.0888</v>
+        <v>0.118</v>
       </c>
       <c r="AF100" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>6</v>
       </c>
       <c r="AJ100" s="3" t="n">
-        <v>0.0122</v>
+        <v>0.0163</v>
       </c>
       <c r="AK100" s="3" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>6</v>
       </c>
       <c r="Z102" t="n">
-        <v>0.394</v>
+        <v>0.368</v>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
@@ -11282,7 +11282,7 @@
         <v>7</v>
       </c>
       <c r="AE102" t="n">
-        <v>0.191</v>
+        <v>0.175</v>
       </c>
       <c r="AF102" t="inlineStr">
         <is>
@@ -11296,7 +11296,7 @@
         <v>5</v>
       </c>
       <c r="AJ102" s="3" t="n">
-        <v>0.0141</v>
+        <v>0.016</v>
       </c>
       <c r="AK102" s="3" t="inlineStr">
         <is>
@@ -11409,7 +11409,7 @@
         <v>8</v>
       </c>
       <c r="AJ103" t="n">
-        <v>0.201</v>
+        <v>0.196</v>
       </c>
       <c r="AK103" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>10</v>
       </c>
       <c r="Z104" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.763</v>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         <v>13</v>
       </c>
       <c r="AE104" t="n">
-        <v>1</v>
+        <v>0.998</v>
       </c>
       <c r="AF104" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
         <v>13</v>
       </c>
       <c r="AJ104" t="n">
-        <v>0.882</v>
+        <v>0.823</v>
       </c>
       <c r="AK104" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>9</v>
       </c>
       <c r="I2" t="n">
-        <v>0.501</v>
+        <v>0.515</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.00118</v>
+        <v>0.00138</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.000163</v>
+        <v>0.000196</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -15676,7 +15676,7 @@
         <v>7</v>
       </c>
       <c r="X2" t="n">
-        <v>0.53</v>
+        <v>0.543</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00255</v>
+        <v>0.00309</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>7</v>
       </c>
       <c r="N3" t="n">
-        <v>0.208</v>
+        <v>0.21</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -15741,7 +15741,7 @@
         <v>3</v>
       </c>
       <c r="S3" t="n">
-        <v>0.00625</v>
+        <v>0.00679</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00121</v>
+        <v>0.00138</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -15792,7 +15792,7 @@
         <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00723</v>
+        <v>0.00795</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>6</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0683</v>
+        <v>0.0697</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>2</v>
       </c>
       <c r="S4" t="n">
-        <v>0.00527</v>
+        <v>0.00594</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>0.00532</v>
+        <v>0.00594</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>7</v>
       </c>
       <c r="I5" t="n">
-        <v>0.431</v>
+        <v>0.442</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>0.00532</v>
+        <v>0.00594</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>7</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0675</v>
+        <v>0.0694</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>9</v>
       </c>
       <c r="X5" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0188</v>
+        <v>0.0195</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>8</v>
       </c>
       <c r="N6" t="n">
-        <v>0.21</v>
+        <v>0.215</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         <v>3</v>
       </c>
       <c r="X6" t="n">
-        <v>0.00537</v>
+        <v>0.00594</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -16029,7 +16029,7 @@
         <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00983</v>
+        <v>0.0105</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>0.00537</v>
+        <v>0.00594</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -16057,7 +16057,7 @@
         <v>9</v>
       </c>
       <c r="S7" t="n">
-        <v>0.899</v>
+        <v>0.907</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -16071,7 +16071,7 @@
         <v>4</v>
       </c>
       <c r="X7" t="n">
-        <v>0.025</v>
+        <v>0.0253</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -16108,7 +16108,7 @@
         <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>0.455</v>
+        <v>0.464</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>5</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0356</v>
+        <v>0.0362</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -16136,7 +16136,7 @@
         <v>4</v>
       </c>
       <c r="S8" t="n">
-        <v>0.00723</v>
+        <v>0.00795</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>6</v>
       </c>
       <c r="X8" t="n">
-        <v>0.501</v>
+        <v>0.515</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -16187,7 +16187,7 @@
         <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>0.11</v>
+        <v>0.109</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -16201,7 +16201,7 @@
         <v>4</v>
       </c>
       <c r="N9" t="n">
-        <v>0.021</v>
+        <v>0.0214</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>8</v>
       </c>
       <c r="S9" t="n">
-        <v>0.21</v>
+        <v>0.215</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -16229,7 +16229,7 @@
         <v>8</v>
       </c>
       <c r="X9" t="n">
-        <v>0.639</v>
+        <v>0.65</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0341</v>
+        <v>0.0338</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
         <v>9</v>
       </c>
       <c r="N10" t="n">
-        <v>0.406</v>
+        <v>0.411</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>6</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0615</v>
+        <v>0.0638</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0849</v>
+        <v>0.0861</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>7</v>
       </c>
       <c r="I12" t="n">
-        <v>0.304</v>
+        <v>0.307</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>0.00261</v>
+        <v>0.00366</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.00404</v>
+        <v>0.00485</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -16388,7 +16388,7 @@
         <v>7</v>
       </c>
       <c r="X12" t="n">
-        <v>0.624</v>
+        <v>0.642</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -16425,7 +16425,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0.00404</v>
+        <v>0.00485</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>9</v>
       </c>
       <c r="N13" t="n">
-        <v>0.743</v>
+        <v>0.753</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -16453,7 +16453,7 @@
         <v>3</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0138</v>
+        <v>0.0146</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -16467,7 +16467,7 @@
         <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>0.00404</v>
+        <v>0.00485</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0198</v>
+        <v>0.0204</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -16518,7 +16518,7 @@
         <v>5</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0519</v>
+        <v>0.0515</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>2</v>
       </c>
       <c r="S14" t="n">
-        <v>0.00894</v>
+        <v>0.0102</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -16546,7 +16546,7 @@
         <v>2</v>
       </c>
       <c r="X14" t="n">
-        <v>0.00404</v>
+        <v>0.00485</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>8</v>
       </c>
       <c r="I15" t="n">
-        <v>0.429</v>
+        <v>0.449</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -16597,7 +16597,7 @@
         <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>0.00404</v>
+        <v>0.00485</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -16611,7 +16611,7 @@
         <v>6</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0832</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -16662,7 +16662,7 @@
         <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>0.00551</v>
+        <v>0.00641</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>0.00597</v>
+        <v>0.00716</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>9</v>
       </c>
       <c r="S16" t="n">
-        <v>0.971</v>
+        <v>0.975</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>3</v>
       </c>
       <c r="X16" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0108</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -16741,7 +16741,7 @@
         <v>6</v>
       </c>
       <c r="I17" t="n">
-        <v>0.143</v>
+        <v>0.142</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0103</v>
+        <v>0.0113</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>8</v>
       </c>
       <c r="X17" t="n">
-        <v>0.971</v>
+        <v>0.975</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0107</v>
+        <v>0.0115</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>7</v>
       </c>
       <c r="N18" t="n">
-        <v>0.174</v>
+        <v>0.171</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>4</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0129</v>
+        <v>0.0138</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -16899,7 +16899,7 @@
         <v>9</v>
       </c>
       <c r="I19" t="n">
-        <v>0.455</v>
+        <v>0.473</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
         <v>6</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0708</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -16927,7 +16927,7 @@
         <v>4</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0177</v>
+        <v>0.0184</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -16941,7 +16941,7 @@
         <v>6</v>
       </c>
       <c r="X19" t="n">
-        <v>0.602</v>
+        <v>0.623</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>5</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0708</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -16992,7 +16992,7 @@
         <v>7</v>
       </c>
       <c r="N20" t="n">
-        <v>0.174</v>
+        <v>0.171</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -17006,7 +17006,7 @@
         <v>7</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0885</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
         <v>5</v>
       </c>
       <c r="X20" t="n">
-        <v>0.109</v>
+        <v>0.111</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
